--- a/WorkBot/refactor/data/orders/Sysco/Sysco_Triphammer_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/Sysco/Sysco_Triphammer_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,6 +821,762 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4617771</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Egg Patty</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>47.08</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>376.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5833462</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Jalapenos (Sliced)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>26.69</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>53.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7128077</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Olive - Kalamata (Pitted)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>51.99</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>51.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1589290</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sausage - Patty (1.5oz)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>24.27</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>291.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2536555</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bacon (Pre-Cooked)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>36.75</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>294.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2916427</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Base - Chicken (No MSG)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>57.47</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>114.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5682919</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Base - Seafood</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>68.65</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>68.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4072666</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Can - Tomato Paste</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>50.95</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>50.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>7256054</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cheddar - Orange (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>38.00</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>228.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>7133036</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Chicken - Diced White &amp; Dark</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>218.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1145283</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Chicken Thigh (Boneless)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>33.25</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>33.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4438911</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Grain Blend 5 Way</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>77.89</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>311.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4828802</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Heavy Cream</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>50.84</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>101.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4579587</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>45.83</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>183.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>9911903</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mayo - Vegan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>95.87</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>95.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7226918</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mozz (Sliced)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>28.75</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>57.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4064978</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mustard - Dijon</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>105.25</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>105.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7770727</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ravioli - Cheese (Med)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>43.65</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>130.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8489148</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Smoked Turkey (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>76.86</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>614.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1796077</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Broccoli Rabe - Fresh</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>51.66</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>103.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1735372</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Cucumber (English)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>13.13</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>39.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2004547</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Herb - Basil (Fresh)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>47.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2252039</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lemon - Fresh</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>37.99</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>37.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1094663</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Onion - Red Jumbo Fresh</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>15.95</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>31.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0683696</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tomato - Fresh Sliced</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>386.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1094721</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Onion - Yellow Fresh</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>5818380</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Can - Coconut Milk</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>92.59</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>185.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3617531</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Roasted Root Vegetables</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>60.69</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>60.69</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
